--- a/UK_CoP_TitleLists/Springer_Open_scifreeimport.xlsx
+++ b/UK_CoP_TitleLists/Springer_Open_scifreeimport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9d4b02a2393526de/Documents/CoP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9D4B02A2393526DE/Documents/CoP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{89CFAB17-42ED-46CB-A8F2-737CA9072434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F91A87F4-E661-4FE6-87F2-24504985906E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87EA2F65-51E7-482F-A0E4-22D5904253D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE44926E-75A4-4EDC-A463-0127E7F3749D}"/>
   </bookViews>
   <sheets>
     <sheet name="Journals" sheetId="5" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4188" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="2105">
   <si>
     <t>Journal Title</t>
   </si>
@@ -6308,13 +6308,61 @@
   </si>
   <si>
     <t>Removed from list - flipped title, hybrid terms</t>
+  </si>
+  <si>
+    <t>EISSN correction to 3091-454X</t>
+  </si>
+  <si>
+    <t>3091-454X</t>
+  </si>
+  <si>
+    <t>EISSN correction to 3091-4531</t>
+  </si>
+  <si>
+    <t>3091-4531</t>
+  </si>
+  <si>
+    <t>Eissn correction to 3091-4523</t>
+  </si>
+  <si>
+    <t>3091-4523</t>
+  </si>
+  <si>
+    <t>Eissn correction to 3091-4507</t>
+  </si>
+  <si>
+    <t>3091-4507</t>
+  </si>
+  <si>
+    <t>Eissn correction to 3091-4515</t>
+  </si>
+  <si>
+    <t>Name &amp; eissn correction Biogeochemical Advances 3091-4493</t>
+  </si>
+  <si>
+    <t>3091-4493</t>
+  </si>
+  <si>
+    <t>Biogeochemical Advances</t>
+  </si>
+  <si>
+    <t>Eissn correction to 3091-3446</t>
+  </si>
+  <si>
+    <t>3091-3446</t>
+  </si>
+  <si>
+    <t>Name change to Psychedelic Substances Research</t>
+  </si>
+  <si>
+    <t>Psychedelic Substances Research</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6357,6 +6405,14 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -6507,10 +6563,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -6549,59 +6606,31 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="9" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -7289,6 +7318,42 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </left>
+        <right style="thin">
+          <color theme="9" tint="-0.499984740745262"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -7308,54 +7373,58 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9D295812-1D4A-459C-A4F4-960C6124B2D7}" name="Table6" displayName="Table6" ref="A1:H621" totalsRowShown="0" headerRowDxfId="0" dataDxfId="31" headerRowBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9D295812-1D4A-459C-A4F4-960C6124B2D7}" name="Table6" displayName="Table6" ref="A1:H621" totalsRowShown="0" headerRowDxfId="31" dataDxfId="29" headerRowBorderDxfId="30">
   <autoFilter ref="A1:H621" xr:uid="{DBD74A84-08EB-4F5A-9B25-A98CF863CE80}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H621">
-    <sortCondition sortBy="cellColor" ref="A1:A621" dxfId="30"/>
+    <sortCondition sortBy="cellColor" ref="A1:A621" dxfId="28"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{9AFFD426-A2FA-45C3-8D93-B3A985635B69}" name="Journal Title" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{B2CF54BD-4659-4AC4-B7EC-272DE1460135}" name="Imprint" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{97894FEA-BB68-4AD8-87BB-7BEA3A095806}" name="Print ISSN"/>
-    <tableColumn id="3" xr3:uid="{9C97C8F0-2986-4610-8CA2-983F2E9C62B2}" name="Electronic ISSN" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{56B65FE1-7786-41FA-9FEF-A5ADCD273C11}" name="Journal URL" dataDxfId="26"/>
-    <tableColumn id="12" xr3:uid="{E7623479-9D70-4D3C-BBE8-EB42E631E813}" name="Publishing Model"/>
-    <tableColumn id="6" xr3:uid="{1F397250-F6F7-4265-8E6E-4D87ECD2D7EC}" name="License Options" dataDxfId="25"/>
-    <tableColumn id="8" xr3:uid="{B4A88968-CE2F-4169-9077-B995EEAD41CB}" name="Subject Areas" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{9AFFD426-A2FA-45C3-8D93-B3A985635B69}" name="Journal Title" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{B2CF54BD-4659-4AC4-B7EC-272DE1460135}" name="Imprint" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{F6967E45-1A6C-41F0-8A9B-236D265E4067}" name="Print ISSN"/>
+    <tableColumn id="3" xr3:uid="{9C97C8F0-2986-4610-8CA2-983F2E9C62B2}" name="Electronic ISSN" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{56B65FE1-7786-41FA-9FEF-A5ADCD273C11}" name="Journal URL" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{B3562423-AE91-4353-B209-5D8137C6D623}" name="Publishing Model"/>
+    <tableColumn id="6" xr3:uid="{1F397250-F6F7-4265-8E6E-4D87ECD2D7EC}" name="License Options" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{B4A88968-CE2F-4169-9077-B995EEAD41CB}" name="Subject Areas" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}" name="Table14" displayName="Table14" ref="A4:J65" totalsRowShown="0" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22" tableBorderDxfId="20" totalsRowBorderDxfId="19">
-  <autoFilter ref="A4:J65" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}" name="Table14" displayName="Table14" ref="A4:J73" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
+  <autoFilter ref="A4:J73" xr:uid="{50DE42A8-741C-4C2A-82B7-4C9C79D7B512}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{1B9A1423-FE7E-41D7-B053-6BF091F459D2}" name="Journal Title" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{B625EB42-AF86-4F71-BC2F-65D99997CD50}" name="Imprint" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{559DDF72-C949-47E4-8DA4-297063A6725C}" name="Print ISSN" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{2C5C0518-FAE9-4E34-9C5C-031EDE4262BA}" name="Electronic ISSN" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{D5474278-5905-4A79-9DFE-DE4AB9980E12}" name="Journal URL" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{3D861C40-F9D7-4168-ACD1-389CE9995730}" name="Publishing Model" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{156C7878-43A4-40BA-84D1-0BD24E590EEE}" name="License Options" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{4C684C0B-6FA6-4E1F-BC47-B228FA209770}" name="Subject Areas" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{96CDE76D-4B76-48A4-98FB-70E2CCC4CFC8}" name="Change Type (See Terms)" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{43B192BA-2299-4882-A245-9C663CF7CF9B}" name="Change Note" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{1B9A1423-FE7E-41D7-B053-6BF091F459D2}" name="Journal Title" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{B625EB42-AF86-4F71-BC2F-65D99997CD50}" name="Imprint" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{559DDF72-C949-47E4-8DA4-297063A6725C}" name="Print ISSN" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{2C5C0518-FAE9-4E34-9C5C-031EDE4262BA}" name="Electronic ISSN" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{D5474278-5905-4A79-9DFE-DE4AB9980E12}" name="Journal URL" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{3D861C40-F9D7-4168-ACD1-389CE9995730}" name="Publishing Model" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{156C7878-43A4-40BA-84D1-0BD24E590EEE}" name="License Options" dataDxfId="10"/>
+    <tableColumn id="8" xr3:uid="{4C684C0B-6FA6-4E1F-BC47-B228FA209770}" name="Subject Areas" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{96CDE76D-4B76-48A4-98FB-70E2CCC4CFC8}" name="Change Type (See Terms)" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{43B192BA-2299-4882-A245-9C663CF7CF9B}" name="Change Note" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}" name="Table25" displayName="Table25" ref="A1:B11" totalsRowShown="0" headerRowDxfId="8" dataDxfId="6" headerRowBorderDxfId="7" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}" name="Table25" displayName="Table25" ref="A1:B11" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A1:B11" xr:uid="{98A0D124-AED4-4DBE-8354-EE3315983F60}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B11">
     <sortCondition ref="A1:A11"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E088FFDE-8F3A-4B84-9B24-F82FF70FAEA5}" name="Term" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{3BB7484B-180C-438A-8248-E8FEA43CCABB}" name="Description" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{E088FFDE-8F3A-4B84-9B24-F82FF70FAEA5}" name="Term" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{3BB7484B-180C-438A-8248-E8FEA43CCABB}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7682,13 +7751,10 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="66" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.7265625" customWidth="1"/>
+    <col min="4" max="6" width="9.81640625" customWidth="1"/>
+    <col min="7" max="7" width="10.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31" x14ac:dyDescent="0.35">
@@ -11525,7 +11591,7 @@
         <v>33</v>
       </c>
       <c r="D192" t="s">
-        <v>669</v>
+        <v>2102</v>
       </c>
       <c r="E192" t="s">
         <v>670</v>
@@ -12539,13 +12605,13 @@
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>840</v>
+        <v>2100</v>
       </c>
       <c r="B243" t="s">
         <v>33</v>
       </c>
       <c r="D243" t="s">
-        <v>841</v>
+        <v>2099</v>
       </c>
       <c r="E243" t="s">
         <v>842</v>
@@ -15985,9 +16051,9 @@
         <v>39</v>
       </c>
       <c r="D415" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E415" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E415" s="20" t="s">
         <v>1418</v>
       </c>
       <c r="F415" t="s">
@@ -16005,7 +16071,7 @@
         <v>39</v>
       </c>
       <c r="D416" t="s">
-        <v>1420</v>
+        <v>2094</v>
       </c>
       <c r="E416" t="s">
         <v>1421</v>
@@ -16025,7 +16091,7 @@
         <v>39</v>
       </c>
       <c r="D417" t="s">
-        <v>1423</v>
+        <v>2090</v>
       </c>
       <c r="E417" t="s">
         <v>1424</v>
@@ -16065,7 +16131,7 @@
         <v>39</v>
       </c>
       <c r="D419" t="s">
-        <v>1429</v>
+        <v>2092</v>
       </c>
       <c r="E419" t="s">
         <v>1430</v>
@@ -18959,7 +19025,7 @@
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1896</v>
+        <v>2104</v>
       </c>
       <c r="B564" t="s">
         <v>33</v>
@@ -20118,16 +20184,19 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E415" r:id="rId1" xr:uid="{40547DF8-518B-47CE-8082-E800BD138B17}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FC2B06-4BD0-4FEC-9578-53390E6CC2F6}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.1796875" style="9" customWidth="1"/>
@@ -20144,30 +20213,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
     </row>
     <row r="4" spans="1:10" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
@@ -21787,14 +21856,241 @@
         <v>2088</v>
       </c>
     </row>
+    <row r="66" spans="1:10" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="15" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H66" s="15"/>
+      <c r="I66" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" customFormat="1" ht="62" x14ac:dyDescent="0.35">
+      <c r="A67" s="15" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67" s="15"/>
+      <c r="I67" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="15" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68" s="15"/>
+      <c r="I68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="15" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69" s="15"/>
+      <c r="I69" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="15" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H70" s="15"/>
+      <c r="I70" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>842</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H71" s="15"/>
+      <c r="I71" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A72" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72" s="15"/>
+      <c r="I72" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="16" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H73" s="16"/>
+      <c r="I73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="25" t="s">
+        <v>2103</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E69" r:id="rId1" xr:uid="{F11F6C94-3C41-4B41-8E91-E8BFDFE79E70}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
